--- a/pageobjects/testData/files/usersCredentials.xlsx
+++ b/pageobjects/testData/files/usersCredentials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="17280" windowHeight="8880"/>
+    <workbookView xWindow="5760" yWindow="1530" windowWidth="17280" windowHeight="8625"/>
   </bookViews>
   <sheets>
     <sheet name="userCredentials" sheetId="7" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>admin</t>
   </si>
@@ -50,9 +50,6 @@
     <t>admin@firstdayhc.com</t>
   </si>
   <si>
-    <t>letsdoit@123</t>
-  </si>
-  <si>
     <t>customerLoginCrendentails</t>
   </si>
   <si>
@@ -62,22 +59,67 @@
     <t>Qwerty@123</t>
   </si>
   <si>
-    <t>testmymanagingprovider7jan@yopmail.com</t>
-  </si>
-  <si>
     <t>FHDAMobileLogin</t>
   </si>
   <si>
     <t>automationWebProvider</t>
   </si>
   <si>
-    <t>ceyoyi9934@ptiong.com</t>
-  </si>
-  <si>
     <t>FHDCMobileLogin</t>
   </si>
   <si>
-    <t>testcaregiver2may@yopmail.com</t>
+    <t>downloadFHDALink</t>
+  </si>
+  <si>
+    <t>downloadFHDCLink</t>
+  </si>
+  <si>
+    <t>customerForStatusCheck</t>
+  </si>
+  <si>
+    <t>Autocustomer@yopmail.com</t>
+  </si>
+  <si>
+    <t>managingProviderForStatusCheck</t>
+  </si>
+  <si>
+    <t>managingautoprovider@yopmail.com</t>
+  </si>
+  <si>
+    <t>testprovider2may@yopmail.com</t>
+  </si>
+  <si>
+    <t>otherProviderForStatusCheck</t>
+  </si>
+  <si>
+    <t>otherautoprovider@yopmail.com</t>
+  </si>
+  <si>
+    <t>providerLoginCrendentails</t>
+  </si>
+  <si>
+    <t>otherProviderForProviderStatusCheck</t>
+  </si>
+  <si>
+    <t>otherautoproviderProv@yopmail.com</t>
+  </si>
+  <si>
+    <t>supreadminautotest@yopmail.com</t>
+  </si>
+  <si>
+    <t>subuserAdmin</t>
+  </si>
+  <si>
+    <t>Kuerty@123</t>
+  </si>
+  <si>
+    <t>caregiverautotest@yopmail.com</t>
+  </si>
+  <si>
+    <t>https://drive.usercontent.google.com/download?id=1hF3YdbxnJsST_p4lx-8PiaPrW9juI90U&amp;export=download&amp;authuser=0</t>
+  </si>
+  <si>
+    <t>https://drive.usercontent.google.com/download?id=1dr2eeOVeQQ3auKsXARELbB810cISIuL3&amp;export=download&amp;authuser=0</t>
   </si>
 </sst>
 </file>
@@ -127,9 +169,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -504,7 +547,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -520,46 +563,134 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
